--- a/api/2/clv3/xlsx/pt/ReportingOrganisation.xlsx
+++ b/api/2/clv3/xlsx/pt/ReportingOrganisation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13968" uniqueCount="5693">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14058" uniqueCount="5725">
   <si>
     <t>code</t>
   </si>
@@ -16690,6 +16690,18 @@
     <t>arin</t>
   </si>
   <si>
+    <t>IN-MHA-231660448</t>
+  </si>
+  <si>
+    <t>ccdc_india</t>
+  </si>
+  <si>
+    <t>TG-NIF-1000047187</t>
+  </si>
+  <si>
+    <t>wildafao</t>
+  </si>
+  <si>
     <t>CH-FDJP-CHE365512867</t>
   </si>
   <si>
@@ -16714,6 +16726,60 @@
     <t>adra-sweden</t>
   </si>
   <si>
+    <t>GB-COH-07921860</t>
+  </si>
+  <si>
+    <t>iigcc</t>
+  </si>
+  <si>
+    <t>MZ-MOJ-100493543</t>
+  </si>
+  <si>
+    <t>apite</t>
+  </si>
+  <si>
+    <t>GB-COH-12075030</t>
+  </si>
+  <si>
+    <t>Private Sector in Provider Country</t>
+  </si>
+  <si>
+    <t>71</t>
+  </si>
+  <si>
+    <t>ica</t>
+  </si>
+  <si>
+    <t>GB-CHC-1111719</t>
+  </si>
+  <si>
+    <t>aaf</t>
+  </si>
+  <si>
+    <t>TZ-NNCB-00NGO00009862</t>
+  </si>
+  <si>
+    <t>mviwanya</t>
+  </si>
+  <si>
+    <t>UA-EDR-45583070</t>
+  </si>
+  <si>
+    <t>vruna</t>
+  </si>
+  <si>
+    <t>XI-ROR-01ej9dk98</t>
+  </si>
+  <si>
+    <t>unimelb</t>
+  </si>
+  <si>
+    <t>TH-MOI-KhorThor3005</t>
+  </si>
+  <si>
+    <t>tlhr</t>
+  </si>
+  <si>
     <t>SE-ON-252002-6135</t>
   </si>
   <si>
@@ -16754,6 +16820,36 @@
   </si>
   <si>
     <t>pangeaafrica</t>
+  </si>
+  <si>
+    <t>ZA-CIP-2025-956558-08</t>
+  </si>
+  <si>
+    <t>iff-npc</t>
+  </si>
+  <si>
+    <t>ZA-CIT-9063151162</t>
+  </si>
+  <si>
+    <t>ukzn</t>
+  </si>
+  <si>
+    <t>MZ-MOJ-821-B</t>
+  </si>
+  <si>
+    <t>asa</t>
+  </si>
+  <si>
+    <t>BR-CNPJ-01567601-0001-43</t>
+  </si>
+  <si>
+    <t>ufg</t>
+  </si>
+  <si>
+    <t>ET-CSA-0067</t>
+  </si>
+  <si>
+    <t>tsda</t>
   </si>
   <si>
     <t>CR-RPJ-3-002-248583</t>
@@ -17424,7 +17520,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2111"/>
+  <dimension ref="A1:G2126"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -62260,16 +62356,16 @@
         <v>9</v>
       </c>
       <c r="D2045" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="E2045" t="s">
-        <v>32</v>
+        <v>176</v>
       </c>
       <c r="F2045" t="s">
         <v>5559</v>
       </c>
       <c r="G2045" t="s">
-        <v>72</v>
+        <v>437</v>
       </c>
     </row>
     <row r="2046" spans="1:7">
@@ -62280,16 +62376,16 @@
         <v>9</v>
       </c>
       <c r="D2046" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="E2046" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="F2046" t="s">
         <v>5561</v>
       </c>
       <c r="G2046" t="s">
-        <v>437</v>
+        <v>4540</v>
       </c>
     </row>
     <row r="2047" spans="1:7">
@@ -62300,16 +62396,16 @@
         <v>9</v>
       </c>
       <c r="D2047" t="s">
-        <v>175</v>
+        <v>31</v>
       </c>
       <c r="E2047" t="s">
-        <v>176</v>
+        <v>32</v>
       </c>
       <c r="F2047" t="s">
         <v>5563</v>
       </c>
       <c r="G2047" t="s">
-        <v>47</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2048" spans="1:7">
@@ -62320,16 +62416,16 @@
         <v>9</v>
       </c>
       <c r="D2048" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="E2048" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="F2048" t="s">
         <v>5565</v>
       </c>
       <c r="G2048" t="s">
-        <v>47</v>
+        <v>437</v>
       </c>
     </row>
     <row r="2049" spans="1:7">
@@ -62340,10 +62436,10 @@
         <v>9</v>
       </c>
       <c r="D2049" t="s">
-        <v>4874</v>
+        <v>175</v>
       </c>
       <c r="E2049" t="s">
-        <v>4875</v>
+        <v>176</v>
       </c>
       <c r="F2049" t="s">
         <v>5567</v>
@@ -62380,10 +62476,10 @@
         <v>9</v>
       </c>
       <c r="D2051" t="s">
-        <v>370</v>
+        <v>37</v>
       </c>
       <c r="E2051" t="s">
-        <v>371</v>
+        <v>38</v>
       </c>
       <c r="F2051" t="s">
         <v>5571</v>
@@ -62400,16 +62496,16 @@
         <v>9</v>
       </c>
       <c r="D2052" t="s">
-        <v>10</v>
+        <v>175</v>
       </c>
       <c r="E2052" t="s">
-        <v>11</v>
+        <v>176</v>
       </c>
       <c r="F2052" t="s">
         <v>5573</v>
       </c>
       <c r="G2052" t="s">
-        <v>47</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="2053" spans="1:7">
@@ -62420,61 +62516,61 @@
         <v>9</v>
       </c>
       <c r="D2053" t="s">
-        <v>370</v>
+        <v>5575</v>
       </c>
       <c r="E2053" t="s">
-        <v>371</v>
+        <v>5576</v>
       </c>
       <c r="F2053" t="s">
-        <v>5575</v>
+        <v>5577</v>
       </c>
       <c r="G2053" t="s">
-        <v>2385</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2054" spans="1:7">
       <c r="A2054" t="s">
-        <v>5576</v>
+        <v>5578</v>
       </c>
       <c r="C2054" t="s">
         <v>9</v>
       </c>
       <c r="D2054" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="E2054" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="F2054" t="s">
-        <v>5577</v>
+        <v>5579</v>
       </c>
       <c r="G2054" t="s">
-        <v>461</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2055" spans="1:7">
       <c r="A2055" t="s">
-        <v>5578</v>
+        <v>5580</v>
       </c>
       <c r="C2055" t="s">
         <v>9</v>
       </c>
       <c r="D2055" t="s">
-        <v>120</v>
+        <v>175</v>
       </c>
       <c r="E2055" t="s">
-        <v>121</v>
+        <v>176</v>
       </c>
       <c r="F2055" t="s">
-        <v>5579</v>
+        <v>5581</v>
       </c>
       <c r="G2055" t="s">
-        <v>706</v>
+        <v>358</v>
       </c>
     </row>
     <row r="2056" spans="1:7">
       <c r="A2056" t="s">
-        <v>5580</v>
+        <v>5582</v>
       </c>
       <c r="C2056" t="s">
         <v>9</v>
@@ -62486,81 +62582,87 @@
         <v>176</v>
       </c>
       <c r="F2056" t="s">
-        <v>5581</v>
+        <v>5583</v>
       </c>
       <c r="G2056" t="s">
-        <v>2867</v>
+        <v>926</v>
       </c>
     </row>
     <row r="2057" spans="1:7">
       <c r="A2057" t="s">
-        <v>5582</v>
+        <v>5584</v>
       </c>
       <c r="C2057" t="s">
         <v>9</v>
       </c>
+      <c r="D2057" t="s">
+        <v>370</v>
+      </c>
+      <c r="E2057" t="s">
+        <v>371</v>
+      </c>
       <c r="F2057" t="s">
-        <v>5583</v>
+        <v>5585</v>
       </c>
       <c r="G2057" t="s">
-        <v>358</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2058" spans="1:7">
       <c r="A2058" t="s">
-        <v>5584</v>
+        <v>5586</v>
       </c>
       <c r="C2058" t="s">
         <v>9</v>
       </c>
       <c r="D2058" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="E2058" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="F2058" t="s">
-        <v>5585</v>
+        <v>5587</v>
       </c>
       <c r="G2058" t="s">
-        <v>634</v>
+        <v>4434</v>
       </c>
     </row>
     <row r="2059" spans="1:7">
       <c r="A2059" t="s">
-        <v>5586</v>
+        <v>5588</v>
       </c>
       <c r="C2059" t="s">
         <v>9</v>
       </c>
       <c r="D2059" t="s">
-        <v>16</v>
+        <v>4874</v>
       </c>
       <c r="E2059" t="s">
-        <v>17</v>
+        <v>4875</v>
       </c>
       <c r="F2059" t="s">
-        <v>5587</v>
+        <v>5589</v>
       </c>
       <c r="G2059" t="s">
-        <v>634</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2060" spans="1:7">
       <c r="A2060" t="s">
-        <v>5588</v>
+        <v>5590</v>
       </c>
       <c r="C2060" t="s">
         <v>9</v>
       </c>
       <c r="D2060" t="s">
-        <v>175</v>
+        <v>31</v>
       </c>
       <c r="E2060" t="s">
-        <v>176</v>
+        <v>32</v>
       </c>
       <c r="F2060" t="s">
-        <v>5589</v>
+        <v>5591</v>
       </c>
       <c r="G2060" t="s">
         <v>47</v>
@@ -62568,39 +62670,39 @@
     </row>
     <row r="2061" spans="1:7">
       <c r="A2061" t="s">
-        <v>5590</v>
+        <v>5592</v>
       </c>
       <c r="C2061" t="s">
         <v>9</v>
       </c>
       <c r="D2061" t="s">
-        <v>5424</v>
+        <v>370</v>
       </c>
       <c r="E2061" t="s">
-        <v>5425</v>
+        <v>371</v>
       </c>
       <c r="F2061" t="s">
-        <v>5591</v>
+        <v>5593</v>
       </c>
       <c r="G2061" t="s">
-        <v>437</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2062" spans="1:7">
       <c r="A2062" t="s">
-        <v>5592</v>
+        <v>5594</v>
       </c>
       <c r="C2062" t="s">
         <v>9</v>
       </c>
       <c r="D2062" t="s">
-        <v>175</v>
+        <v>10</v>
       </c>
       <c r="E2062" t="s">
-        <v>176</v>
+        <v>11</v>
       </c>
       <c r="F2062" t="s">
-        <v>5593</v>
+        <v>5595</v>
       </c>
       <c r="G2062" t="s">
         <v>47</v>
@@ -62608,135 +62710,147 @@
     </row>
     <row r="2063" spans="1:7">
       <c r="A2063" t="s">
-        <v>5594</v>
+        <v>5596</v>
       </c>
       <c r="C2063" t="s">
         <v>9</v>
       </c>
+      <c r="D2063" t="s">
+        <v>370</v>
+      </c>
+      <c r="E2063" t="s">
+        <v>371</v>
+      </c>
       <c r="F2063" t="s">
-        <v>5595</v>
+        <v>5597</v>
       </c>
       <c r="G2063" t="s">
-        <v>47</v>
+        <v>2385</v>
       </c>
     </row>
     <row r="2064" spans="1:7">
       <c r="A2064" t="s">
-        <v>5596</v>
+        <v>5598</v>
       </c>
       <c r="C2064" t="s">
         <v>9</v>
       </c>
       <c r="D2064" t="s">
-        <v>120</v>
+        <v>31</v>
       </c>
       <c r="E2064" t="s">
-        <v>121</v>
+        <v>32</v>
       </c>
       <c r="F2064" t="s">
-        <v>5597</v>
+        <v>5599</v>
       </c>
       <c r="G2064" t="s">
-        <v>4434</v>
+        <v>461</v>
       </c>
     </row>
     <row r="2065" spans="1:7">
       <c r="A2065" t="s">
-        <v>5598</v>
+        <v>5600</v>
       </c>
       <c r="C2065" t="s">
         <v>9</v>
       </c>
       <c r="D2065" t="s">
-        <v>175</v>
+        <v>120</v>
       </c>
       <c r="E2065" t="s">
-        <v>176</v>
+        <v>121</v>
       </c>
       <c r="F2065" t="s">
-        <v>5599</v>
+        <v>5601</v>
       </c>
       <c r="G2065" t="s">
-        <v>403</v>
+        <v>706</v>
       </c>
     </row>
     <row r="2066" spans="1:7">
       <c r="A2066" t="s">
-        <v>5600</v>
+        <v>5602</v>
       </c>
       <c r="C2066" t="s">
         <v>9</v>
       </c>
       <c r="D2066" t="s">
-        <v>22</v>
+        <v>4874</v>
       </c>
       <c r="E2066" t="s">
-        <v>23</v>
+        <v>4875</v>
       </c>
       <c r="F2066" t="s">
-        <v>5601</v>
+        <v>5603</v>
       </c>
       <c r="G2066" t="s">
-        <v>47</v>
+        <v>293</v>
       </c>
     </row>
     <row r="2067" spans="1:7">
       <c r="A2067" t="s">
-        <v>5602</v>
+        <v>5604</v>
       </c>
       <c r="C2067" t="s">
         <v>9</v>
       </c>
       <c r="D2067" t="s">
-        <v>31</v>
+        <v>370</v>
       </c>
       <c r="E2067" t="s">
-        <v>32</v>
+        <v>371</v>
       </c>
       <c r="F2067" t="s">
-        <v>5603</v>
+        <v>5605</v>
       </c>
       <c r="G2067" t="s">
-        <v>482</v>
+        <v>293</v>
       </c>
     </row>
     <row r="2068" spans="1:7">
       <c r="A2068" t="s">
-        <v>5604</v>
+        <v>5606</v>
       </c>
       <c r="C2068" t="s">
         <v>9</v>
       </c>
       <c r="D2068" t="s">
-        <v>4874</v>
+        <v>5424</v>
       </c>
       <c r="E2068" t="s">
-        <v>4875</v>
+        <v>5425</v>
       </c>
       <c r="F2068" t="s">
-        <v>5605</v>
+        <v>5607</v>
       </c>
       <c r="G2068" t="s">
-        <v>5606</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="2069" spans="1:7">
       <c r="A2069" t="s">
-        <v>5607</v>
+        <v>5608</v>
       </c>
       <c r="C2069" t="s">
         <v>9</v>
       </c>
+      <c r="D2069" t="s">
+        <v>370</v>
+      </c>
+      <c r="E2069" t="s">
+        <v>371</v>
+      </c>
       <c r="F2069" t="s">
-        <v>5608</v>
+        <v>5609</v>
       </c>
       <c r="G2069" t="s">
-        <v>47</v>
+        <v>4262</v>
       </c>
     </row>
     <row r="2070" spans="1:7">
       <c r="A2070" t="s">
-        <v>5609</v>
+        <v>5610</v>
       </c>
       <c r="C2070" t="s">
         <v>9</v>
@@ -62748,107 +62862,101 @@
         <v>176</v>
       </c>
       <c r="F2070" t="s">
-        <v>5610</v>
+        <v>5611</v>
       </c>
       <c r="G2070" t="s">
-        <v>684</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="2071" spans="1:7">
       <c r="A2071" t="s">
-        <v>5611</v>
+        <v>5612</v>
       </c>
       <c r="C2071" t="s">
         <v>9</v>
       </c>
       <c r="D2071" t="s">
-        <v>10</v>
+        <v>175</v>
       </c>
       <c r="E2071" t="s">
-        <v>11</v>
+        <v>176</v>
       </c>
       <c r="F2071" t="s">
-        <v>5612</v>
+        <v>5613</v>
       </c>
       <c r="G2071" t="s">
-        <v>504</v>
+        <v>2867</v>
       </c>
     </row>
     <row r="2072" spans="1:7">
       <c r="A2072" t="s">
-        <v>5613</v>
+        <v>5614</v>
       </c>
       <c r="C2072" t="s">
         <v>9</v>
       </c>
-      <c r="D2072" t="s">
-        <v>175</v>
-      </c>
-      <c r="E2072" t="s">
-        <v>176</v>
-      </c>
       <c r="F2072" t="s">
-        <v>5614</v>
+        <v>5615</v>
       </c>
       <c r="G2072" t="s">
-        <v>600</v>
+        <v>358</v>
       </c>
     </row>
     <row r="2073" spans="1:7">
       <c r="A2073" t="s">
-        <v>5615</v>
+        <v>5616</v>
       </c>
       <c r="C2073" t="s">
         <v>9</v>
       </c>
       <c r="D2073" t="s">
-        <v>175</v>
+        <v>31</v>
       </c>
       <c r="E2073" t="s">
-        <v>176</v>
+        <v>32</v>
       </c>
       <c r="F2073" t="s">
-        <v>5616</v>
+        <v>5617</v>
       </c>
       <c r="G2073" t="s">
-        <v>437</v>
+        <v>634</v>
       </c>
     </row>
     <row r="2074" spans="1:7">
       <c r="A2074" t="s">
-        <v>5617</v>
+        <v>5618</v>
       </c>
       <c r="C2074" t="s">
         <v>9</v>
       </c>
       <c r="D2074" t="s">
-        <v>120</v>
+        <v>16</v>
       </c>
       <c r="E2074" t="s">
-        <v>121</v>
+        <v>17</v>
       </c>
       <c r="F2074" t="s">
-        <v>5618</v>
+        <v>5619</v>
       </c>
       <c r="G2074" t="s">
-        <v>87</v>
+        <v>634</v>
       </c>
     </row>
     <row r="2075" spans="1:7">
       <c r="A2075" t="s">
-        <v>5619</v>
+        <v>5620</v>
       </c>
       <c r="C2075" t="s">
         <v>9</v>
       </c>
       <c r="D2075" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="E2075" t="s">
-        <v>32</v>
+        <v>176</v>
       </c>
       <c r="F2075" t="s">
-        <v>5620</v>
+        <v>5621</v>
       </c>
       <c r="G2075" t="s">
         <v>47</v>
@@ -62856,27 +62964,27 @@
     </row>
     <row r="2076" spans="1:7">
       <c r="A2076" t="s">
-        <v>5621</v>
+        <v>5622</v>
       </c>
       <c r="C2076" t="s">
         <v>9</v>
       </c>
       <c r="D2076" t="s">
-        <v>22</v>
+        <v>5424</v>
       </c>
       <c r="E2076" t="s">
-        <v>23</v>
+        <v>5425</v>
       </c>
       <c r="F2076" t="s">
-        <v>5622</v>
+        <v>5623</v>
       </c>
       <c r="G2076" t="s">
-        <v>47</v>
+        <v>437</v>
       </c>
     </row>
     <row r="2077" spans="1:7">
       <c r="A2077" t="s">
-        <v>5623</v>
+        <v>5624</v>
       </c>
       <c r="C2077" t="s">
         <v>9</v>
@@ -62888,135 +62996,135 @@
         <v>176</v>
       </c>
       <c r="F2077" t="s">
-        <v>5624</v>
+        <v>5625</v>
       </c>
       <c r="G2077" t="s">
-        <v>1998</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2078" spans="1:7">
       <c r="A2078" t="s">
-        <v>5625</v>
+        <v>5626</v>
       </c>
       <c r="C2078" t="s">
         <v>9</v>
       </c>
-      <c r="D2078" t="s">
-        <v>370</v>
-      </c>
-      <c r="E2078" t="s">
-        <v>371</v>
-      </c>
       <c r="F2078" t="s">
-        <v>5626</v>
+        <v>5627</v>
       </c>
       <c r="G2078" t="s">
-        <v>600</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2079" spans="1:7">
       <c r="A2079" t="s">
-        <v>5627</v>
+        <v>5628</v>
       </c>
       <c r="C2079" t="s">
         <v>9</v>
       </c>
       <c r="D2079" t="s">
-        <v>175</v>
+        <v>120</v>
       </c>
       <c r="E2079" t="s">
-        <v>176</v>
+        <v>121</v>
       </c>
       <c r="F2079" t="s">
-        <v>5628</v>
+        <v>5629</v>
       </c>
       <c r="G2079" t="s">
-        <v>1924</v>
+        <v>4434</v>
       </c>
     </row>
     <row r="2080" spans="1:7">
       <c r="A2080" t="s">
-        <v>5629</v>
+        <v>5630</v>
       </c>
       <c r="C2080" t="s">
         <v>9</v>
       </c>
+      <c r="D2080" t="s">
+        <v>175</v>
+      </c>
+      <c r="E2080" t="s">
+        <v>176</v>
+      </c>
       <c r="F2080" t="s">
-        <v>5630</v>
+        <v>5631</v>
       </c>
       <c r="G2080" t="s">
-        <v>706</v>
+        <v>403</v>
       </c>
     </row>
     <row r="2081" spans="1:7">
       <c r="A2081" t="s">
-        <v>5631</v>
+        <v>5632</v>
       </c>
       <c r="C2081" t="s">
         <v>9</v>
       </c>
       <c r="D2081" t="s">
-        <v>370</v>
+        <v>22</v>
       </c>
       <c r="E2081" t="s">
-        <v>371</v>
+        <v>23</v>
       </c>
       <c r="F2081" t="s">
-        <v>5632</v>
+        <v>5633</v>
       </c>
       <c r="G2081" t="s">
-        <v>471</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2082" spans="1:7">
       <c r="A2082" t="s">
-        <v>5633</v>
+        <v>5634</v>
       </c>
       <c r="C2082" t="s">
         <v>9</v>
       </c>
       <c r="D2082" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="E2082" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="F2082" t="s">
-        <v>5634</v>
+        <v>5635</v>
       </c>
       <c r="G2082" t="s">
-        <v>34</v>
+        <v>482</v>
       </c>
     </row>
     <row r="2083" spans="1:7">
       <c r="A2083" t="s">
-        <v>5635</v>
+        <v>5636</v>
       </c>
       <c r="C2083" t="s">
         <v>9</v>
       </c>
       <c r="D2083" t="s">
-        <v>370</v>
+        <v>4874</v>
       </c>
       <c r="E2083" t="s">
-        <v>371</v>
+        <v>4875</v>
       </c>
       <c r="F2083" t="s">
-        <v>5636</v>
+        <v>5637</v>
       </c>
       <c r="G2083" t="s">
-        <v>34</v>
+        <v>5638</v>
       </c>
     </row>
     <row r="2084" spans="1:7">
       <c r="A2084" t="s">
-        <v>5637</v>
+        <v>5639</v>
       </c>
       <c r="C2084" t="s">
         <v>9</v>
       </c>
       <c r="F2084" t="s">
-        <v>5638</v>
+        <v>5640</v>
       </c>
       <c r="G2084" t="s">
         <v>47</v>
@@ -63024,7 +63132,7 @@
     </row>
     <row r="2085" spans="1:7">
       <c r="A2085" t="s">
-        <v>5639</v>
+        <v>5641</v>
       </c>
       <c r="C2085" t="s">
         <v>9</v>
@@ -63036,35 +63144,35 @@
         <v>176</v>
       </c>
       <c r="F2085" t="s">
-        <v>5640</v>
+        <v>5642</v>
       </c>
       <c r="G2085" t="s">
-        <v>2495</v>
+        <v>684</v>
       </c>
     </row>
     <row r="2086" spans="1:7">
       <c r="A2086" t="s">
-        <v>5641</v>
+        <v>5643</v>
       </c>
       <c r="C2086" t="s">
         <v>9</v>
       </c>
       <c r="D2086" t="s">
-        <v>175</v>
+        <v>10</v>
       </c>
       <c r="E2086" t="s">
-        <v>176</v>
+        <v>11</v>
       </c>
       <c r="F2086" t="s">
-        <v>5642</v>
+        <v>5644</v>
       </c>
       <c r="G2086" t="s">
-        <v>47</v>
+        <v>504</v>
       </c>
     </row>
     <row r="2087" spans="1:7">
       <c r="A2087" t="s">
-        <v>5643</v>
+        <v>5645</v>
       </c>
       <c r="C2087" t="s">
         <v>9</v>
@@ -63076,129 +63184,135 @@
         <v>176</v>
       </c>
       <c r="F2087" t="s">
-        <v>5644</v>
+        <v>5646</v>
       </c>
       <c r="G2087" t="s">
-        <v>47</v>
+        <v>600</v>
       </c>
     </row>
     <row r="2088" spans="1:7">
       <c r="A2088" t="s">
-        <v>5645</v>
+        <v>5647</v>
       </c>
       <c r="C2088" t="s">
         <v>9</v>
       </c>
       <c r="D2088" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="E2088" t="s">
-        <v>32</v>
+        <v>176</v>
       </c>
       <c r="F2088" t="s">
-        <v>5646</v>
+        <v>5648</v>
       </c>
       <c r="G2088" t="s">
-        <v>47</v>
+        <v>437</v>
       </c>
     </row>
     <row r="2089" spans="1:7">
       <c r="A2089" t="s">
-        <v>5647</v>
+        <v>5649</v>
       </c>
       <c r="C2089" t="s">
         <v>9</v>
       </c>
       <c r="D2089" t="s">
-        <v>175</v>
+        <v>120</v>
       </c>
       <c r="E2089" t="s">
-        <v>176</v>
+        <v>121</v>
       </c>
       <c r="F2089" t="s">
-        <v>5648</v>
+        <v>5650</v>
       </c>
       <c r="G2089" t="s">
-        <v>926</v>
+        <v>87</v>
       </c>
     </row>
     <row r="2090" spans="1:7">
       <c r="A2090" t="s">
-        <v>5649</v>
+        <v>5651</v>
       </c>
       <c r="C2090" t="s">
         <v>9</v>
       </c>
+      <c r="D2090" t="s">
+        <v>31</v>
+      </c>
+      <c r="E2090" t="s">
+        <v>32</v>
+      </c>
       <c r="F2090" t="s">
-        <v>5650</v>
+        <v>5652</v>
       </c>
       <c r="G2090" t="s">
-        <v>437</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2091" spans="1:7">
       <c r="A2091" t="s">
-        <v>5651</v>
+        <v>5653</v>
       </c>
       <c r="C2091" t="s">
         <v>9</v>
       </c>
       <c r="D2091" t="s">
-        <v>370</v>
+        <v>22</v>
       </c>
       <c r="E2091" t="s">
-        <v>371</v>
+        <v>23</v>
       </c>
       <c r="F2091" t="s">
-        <v>5652</v>
+        <v>5654</v>
       </c>
       <c r="G2091" t="s">
-        <v>3605</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2092" spans="1:7">
       <c r="A2092" t="s">
-        <v>5653</v>
+        <v>5655</v>
       </c>
       <c r="C2092" t="s">
         <v>9</v>
       </c>
       <c r="D2092" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="E2092" t="s">
-        <v>32</v>
+        <v>176</v>
       </c>
       <c r="F2092" t="s">
-        <v>5654</v>
+        <v>5656</v>
       </c>
       <c r="G2092" t="s">
-        <v>25</v>
+        <v>1998</v>
       </c>
     </row>
     <row r="2093" spans="1:7">
       <c r="A2093" t="s">
-        <v>5655</v>
+        <v>5657</v>
       </c>
       <c r="C2093" t="s">
         <v>9</v>
       </c>
       <c r="D2093" t="s">
-        <v>175</v>
+        <v>370</v>
       </c>
       <c r="E2093" t="s">
-        <v>176</v>
+        <v>371</v>
       </c>
       <c r="F2093" t="s">
-        <v>5656</v>
+        <v>5658</v>
       </c>
       <c r="G2093" t="s">
-        <v>1908</v>
+        <v>600</v>
       </c>
     </row>
     <row r="2094" spans="1:7">
       <c r="A2094" t="s">
-        <v>5657</v>
+        <v>5659</v>
       </c>
       <c r="C2094" t="s">
         <v>9</v>
@@ -63210,121 +63324,115 @@
         <v>176</v>
       </c>
       <c r="F2094" t="s">
-        <v>5658</v>
+        <v>5660</v>
       </c>
       <c r="G2094" t="s">
-        <v>5606</v>
+        <v>1924</v>
       </c>
     </row>
     <row r="2095" spans="1:7">
       <c r="A2095" t="s">
-        <v>5659</v>
+        <v>5661</v>
       </c>
       <c r="C2095" t="s">
         <v>9</v>
       </c>
-      <c r="D2095" t="s">
-        <v>175</v>
-      </c>
-      <c r="E2095" t="s">
-        <v>176</v>
-      </c>
       <c r="F2095" t="s">
-        <v>5660</v>
+        <v>5662</v>
       </c>
       <c r="G2095" t="s">
-        <v>5545</v>
+        <v>706</v>
       </c>
     </row>
     <row r="2096" spans="1:7">
       <c r="A2096" t="s">
-        <v>5661</v>
+        <v>5663</v>
       </c>
       <c r="C2096" t="s">
         <v>9</v>
       </c>
+      <c r="D2096" t="s">
+        <v>370</v>
+      </c>
+      <c r="E2096" t="s">
+        <v>371</v>
+      </c>
       <c r="F2096" t="s">
-        <v>5662</v>
+        <v>5664</v>
       </c>
       <c r="G2096" t="s">
-        <v>47</v>
+        <v>471</v>
       </c>
     </row>
     <row r="2097" spans="1:7">
       <c r="A2097" t="s">
-        <v>5663</v>
+        <v>5665</v>
       </c>
       <c r="C2097" t="s">
         <v>9</v>
       </c>
       <c r="D2097" t="s">
-        <v>120</v>
+        <v>22</v>
       </c>
       <c r="E2097" t="s">
-        <v>121</v>
+        <v>23</v>
       </c>
       <c r="F2097" t="s">
-        <v>5664</v>
+        <v>5666</v>
       </c>
       <c r="G2097" t="s">
-        <v>358</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2098" spans="1:7">
       <c r="A2098" t="s">
-        <v>5665</v>
+        <v>5667</v>
       </c>
       <c r="C2098" t="s">
         <v>9</v>
       </c>
       <c r="D2098" t="s">
-        <v>175</v>
+        <v>370</v>
       </c>
       <c r="E2098" t="s">
-        <v>176</v>
+        <v>371</v>
       </c>
       <c r="F2098" t="s">
-        <v>5666</v>
+        <v>5668</v>
       </c>
       <c r="G2098" t="s">
-        <v>926</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2099" spans="1:7">
       <c r="A2099" t="s">
-        <v>5667</v>
+        <v>5669</v>
       </c>
       <c r="C2099" t="s">
         <v>9</v>
       </c>
-      <c r="D2099" t="s">
-        <v>370</v>
-      </c>
-      <c r="E2099" t="s">
-        <v>371</v>
-      </c>
       <c r="F2099" t="s">
-        <v>5668</v>
+        <v>5670</v>
       </c>
       <c r="G2099" t="s">
-        <v>1686</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2100" spans="1:7">
       <c r="A2100" t="s">
-        <v>5669</v>
+        <v>5671</v>
       </c>
       <c r="C2100" t="s">
         <v>9</v>
       </c>
       <c r="D2100" t="s">
-        <v>22</v>
+        <v>175</v>
       </c>
       <c r="E2100" t="s">
-        <v>23</v>
+        <v>176</v>
       </c>
       <c r="F2100" t="s">
-        <v>5670</v>
+        <v>5672</v>
       </c>
       <c r="G2100" t="s">
         <v>2495</v>
@@ -63332,7 +63440,7 @@
     </row>
     <row r="2101" spans="1:7">
       <c r="A2101" t="s">
-        <v>5671</v>
+        <v>5673</v>
       </c>
       <c r="C2101" t="s">
         <v>9</v>
@@ -63344,35 +63452,35 @@
         <v>176</v>
       </c>
       <c r="F2101" t="s">
-        <v>5672</v>
+        <v>5674</v>
       </c>
       <c r="G2101" t="s">
-        <v>2791</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2102" spans="1:7">
       <c r="A2102" t="s">
-        <v>5673</v>
+        <v>5675</v>
       </c>
       <c r="C2102" t="s">
         <v>9</v>
       </c>
       <c r="D2102" t="s">
-        <v>10</v>
+        <v>175</v>
       </c>
       <c r="E2102" t="s">
-        <v>11</v>
+        <v>176</v>
       </c>
       <c r="F2102" t="s">
-        <v>5674</v>
+        <v>5676</v>
       </c>
       <c r="G2102" t="s">
-        <v>5295</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2103" spans="1:7">
       <c r="A2103" t="s">
-        <v>5675</v>
+        <v>5677</v>
       </c>
       <c r="C2103" t="s">
         <v>9</v>
@@ -63384,7 +63492,7 @@
         <v>32</v>
       </c>
       <c r="F2103" t="s">
-        <v>5676</v>
+        <v>5678</v>
       </c>
       <c r="G2103" t="s">
         <v>47</v>
@@ -63392,87 +63500,81 @@
     </row>
     <row r="2104" spans="1:7">
       <c r="A2104" t="s">
-        <v>5677</v>
+        <v>5679</v>
       </c>
       <c r="C2104" t="s">
         <v>9</v>
       </c>
       <c r="D2104" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="E2104" t="s">
-        <v>32</v>
+        <v>176</v>
       </c>
       <c r="F2104" t="s">
-        <v>5678</v>
+        <v>5680</v>
       </c>
       <c r="G2104" t="s">
-        <v>47</v>
+        <v>926</v>
       </c>
     </row>
     <row r="2105" spans="1:7">
       <c r="A2105" t="s">
-        <v>5679</v>
+        <v>5681</v>
       </c>
       <c r="C2105" t="s">
         <v>9</v>
       </c>
-      <c r="D2105" t="s">
-        <v>31</v>
-      </c>
-      <c r="E2105" t="s">
-        <v>32</v>
-      </c>
       <c r="F2105" t="s">
-        <v>5680</v>
+        <v>5682</v>
       </c>
       <c r="G2105" t="s">
-        <v>47</v>
+        <v>437</v>
       </c>
     </row>
     <row r="2106" spans="1:7">
       <c r="A2106" t="s">
-        <v>5681</v>
+        <v>5683</v>
       </c>
       <c r="C2106" t="s">
         <v>9</v>
       </c>
       <c r="D2106" t="s">
-        <v>22</v>
+        <v>370</v>
       </c>
       <c r="E2106" t="s">
-        <v>23</v>
+        <v>371</v>
       </c>
       <c r="F2106" t="s">
-        <v>5682</v>
+        <v>5684</v>
       </c>
       <c r="G2106" t="s">
-        <v>47</v>
+        <v>3605</v>
       </c>
     </row>
     <row r="2107" spans="1:7">
       <c r="A2107" t="s">
-        <v>5683</v>
+        <v>5685</v>
       </c>
       <c r="C2107" t="s">
         <v>9</v>
       </c>
       <c r="D2107" t="s">
-        <v>290</v>
+        <v>31</v>
       </c>
       <c r="E2107" t="s">
-        <v>291</v>
+        <v>32</v>
       </c>
       <c r="F2107" t="s">
-        <v>5684</v>
+        <v>5686</v>
       </c>
       <c r="G2107" t="s">
-        <v>437</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2108" spans="1:7">
       <c r="A2108" t="s">
-        <v>5685</v>
+        <v>5687</v>
       </c>
       <c r="C2108" t="s">
         <v>9</v>
@@ -63484,72 +63586,366 @@
         <v>176</v>
       </c>
       <c r="F2108" t="s">
-        <v>5686</v>
+        <v>5688</v>
       </c>
       <c r="G2108" t="s">
-        <v>358</v>
+        <v>1908</v>
       </c>
     </row>
     <row r="2109" spans="1:7">
       <c r="A2109" t="s">
-        <v>5687</v>
+        <v>5689</v>
       </c>
       <c r="C2109" t="s">
         <v>9</v>
       </c>
       <c r="D2109" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="E2109" t="s">
-        <v>32</v>
+        <v>176</v>
       </c>
       <c r="F2109" t="s">
-        <v>5688</v>
+        <v>5690</v>
       </c>
       <c r="G2109" t="s">
-        <v>47</v>
+        <v>5638</v>
       </c>
     </row>
     <row r="2110" spans="1:7">
       <c r="A2110" t="s">
-        <v>5689</v>
+        <v>5691</v>
       </c>
       <c r="C2110" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="D2110" t="s">
-        <v>290</v>
+        <v>175</v>
       </c>
       <c r="E2110" t="s">
-        <v>291</v>
+        <v>176</v>
       </c>
       <c r="F2110" t="s">
-        <v>4750</v>
+        <v>5692</v>
       </c>
       <c r="G2110" t="s">
-        <v>1686</v>
+        <v>5545</v>
       </c>
     </row>
     <row r="2111" spans="1:7">
       <c r="A2111" t="s">
-        <v>5690</v>
-      </c>
-      <c r="B2111" t="s">
-        <v>5691</v>
+        <v>5693</v>
       </c>
       <c r="C2111" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2111" t="s">
+        <v>5694</v>
+      </c>
+      <c r="G2111" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2112" spans="1:7">
+      <c r="A2112" t="s">
+        <v>5695</v>
+      </c>
+      <c r="C2112" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2112" t="s">
+        <v>120</v>
+      </c>
+      <c r="E2112" t="s">
+        <v>121</v>
+      </c>
+      <c r="F2112" t="s">
+        <v>5696</v>
+      </c>
+      <c r="G2112" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="2113" spans="1:7">
+      <c r="A2113" t="s">
+        <v>5697</v>
+      </c>
+      <c r="C2113" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2113" t="s">
+        <v>175</v>
+      </c>
+      <c r="E2113" t="s">
+        <v>176</v>
+      </c>
+      <c r="F2113" t="s">
+        <v>5698</v>
+      </c>
+      <c r="G2113" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="2114" spans="1:7">
+      <c r="A2114" t="s">
+        <v>5699</v>
+      </c>
+      <c r="C2114" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2114" t="s">
+        <v>370</v>
+      </c>
+      <c r="E2114" t="s">
+        <v>371</v>
+      </c>
+      <c r="F2114" t="s">
+        <v>5700</v>
+      </c>
+      <c r="G2114" t="s">
+        <v>1686</v>
+      </c>
+    </row>
+    <row r="2115" spans="1:7">
+      <c r="A2115" t="s">
+        <v>5701</v>
+      </c>
+      <c r="C2115" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2115" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2115" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2115" t="s">
+        <v>5702</v>
+      </c>
+      <c r="G2115" t="s">
+        <v>2495</v>
+      </c>
+    </row>
+    <row r="2116" spans="1:7">
+      <c r="A2116" t="s">
+        <v>5703</v>
+      </c>
+      <c r="C2116" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2116" t="s">
+        <v>175</v>
+      </c>
+      <c r="E2116" t="s">
+        <v>176</v>
+      </c>
+      <c r="F2116" t="s">
+        <v>5704</v>
+      </c>
+      <c r="G2116" t="s">
+        <v>2791</v>
+      </c>
+    </row>
+    <row r="2117" spans="1:7">
+      <c r="A2117" t="s">
+        <v>5705</v>
+      </c>
+      <c r="C2117" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2117" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2117" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2117" t="s">
+        <v>5706</v>
+      </c>
+      <c r="G2117" t="s">
+        <v>5295</v>
+      </c>
+    </row>
+    <row r="2118" spans="1:7">
+      <c r="A2118" t="s">
+        <v>5707</v>
+      </c>
+      <c r="C2118" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2118" t="s">
+        <v>31</v>
+      </c>
+      <c r="E2118" t="s">
+        <v>32</v>
+      </c>
+      <c r="F2118" t="s">
+        <v>5708</v>
+      </c>
+      <c r="G2118" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2119" spans="1:7">
+      <c r="A2119" t="s">
+        <v>5709</v>
+      </c>
+      <c r="C2119" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2119" t="s">
+        <v>31</v>
+      </c>
+      <c r="E2119" t="s">
+        <v>32</v>
+      </c>
+      <c r="F2119" t="s">
+        <v>5710</v>
+      </c>
+      <c r="G2119" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2120" spans="1:7">
+      <c r="A2120" t="s">
+        <v>5711</v>
+      </c>
+      <c r="C2120" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2120" t="s">
+        <v>31</v>
+      </c>
+      <c r="E2120" t="s">
+        <v>32</v>
+      </c>
+      <c r="F2120" t="s">
+        <v>5712</v>
+      </c>
+      <c r="G2120" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2121" spans="1:7">
+      <c r="A2121" t="s">
+        <v>5713</v>
+      </c>
+      <c r="C2121" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2121" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2121" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2121" t="s">
+        <v>5714</v>
+      </c>
+      <c r="G2121" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2122" spans="1:7">
+      <c r="A2122" t="s">
+        <v>5715</v>
+      </c>
+      <c r="C2122" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2122" t="s">
+        <v>290</v>
+      </c>
+      <c r="E2122" t="s">
+        <v>291</v>
+      </c>
+      <c r="F2122" t="s">
+        <v>5716</v>
+      </c>
+      <c r="G2122" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="2123" spans="1:7">
+      <c r="A2123" t="s">
+        <v>5717</v>
+      </c>
+      <c r="C2123" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2123" t="s">
+        <v>175</v>
+      </c>
+      <c r="E2123" t="s">
+        <v>176</v>
+      </c>
+      <c r="F2123" t="s">
+        <v>5718</v>
+      </c>
+      <c r="G2123" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="2124" spans="1:7">
+      <c r="A2124" t="s">
+        <v>5719</v>
+      </c>
+      <c r="C2124" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2124" t="s">
+        <v>31</v>
+      </c>
+      <c r="E2124" t="s">
+        <v>32</v>
+      </c>
+      <c r="F2124" t="s">
+        <v>5720</v>
+      </c>
+      <c r="G2124" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2125" spans="1:7">
+      <c r="A2125" t="s">
+        <v>5721</v>
+      </c>
+      <c r="C2125" t="s">
         <v>42</v>
       </c>
-      <c r="D2111" t="s">
+      <c r="D2125" t="s">
+        <v>290</v>
+      </c>
+      <c r="E2125" t="s">
+        <v>291</v>
+      </c>
+      <c r="F2125" t="s">
+        <v>4750</v>
+      </c>
+      <c r="G2125" t="s">
+        <v>1686</v>
+      </c>
+    </row>
+    <row r="2126" spans="1:7">
+      <c r="A2126" t="s">
+        <v>5722</v>
+      </c>
+      <c r="B2126" t="s">
+        <v>5723</v>
+      </c>
+      <c r="C2126" t="s">
+        <v>42</v>
+      </c>
+      <c r="D2126" t="s">
         <v>370</v>
       </c>
-      <c r="E2111" t="s">
+      <c r="E2126" t="s">
         <v>371</v>
       </c>
-      <c r="F2111" t="s">
-        <v>5692</v>
-      </c>
-      <c r="G2111" t="s">
+      <c r="F2126" t="s">
+        <v>5724</v>
+      </c>
+      <c r="G2126" t="s">
         <v>525</v>
       </c>
     </row>
